--- a/reports/analytics/q06_most_affected_population_groups.xlsx
+++ b/reports/analytics/q06_most_affected_population_groups.xlsx
@@ -1663,16 +1663,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1705,16 +1705,16 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1768,16 +1768,16 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1789,16 +1789,16 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1957,42 +1957,42 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2776,42 +2776,42 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3158,70 +3158,70 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3231,14 +3231,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -3247,61 +3247,61 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -3343,28 +3343,28 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -3373,19 +3373,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -3394,54 +3394,54 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3469,11 +3469,11 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3490,7 +3490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3511,16 +3511,16 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3532,16 +3532,16 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3553,16 +3553,16 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3574,16 +3574,16 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3595,11 +3595,11 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3637,42 +3637,42 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3700,11 +3700,11 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3714,60 +3714,60 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3784,28 +3784,28 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -3847,11 +3847,11 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3861,44 +3861,44 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3910,32 +3910,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3945,44 +3945,44 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3994,79 +3994,79 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4078,28 +4078,28 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -4113,28 +4113,28 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4155,39 +4155,39 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -4477,11 +4477,11 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4491,18 +4491,18 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -4624,42 +4624,42 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -5611,11 +5611,11 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5625,18 +5625,18 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5646,18 +5646,18 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5667,14 +5667,14 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -5683,44 +5683,44 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -5746,19 +5746,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -5767,23 +5767,23 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5800,42 +5800,42 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -6010,16 +6010,16 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6031,16 +6031,16 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6220,7 +6220,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -6234,14 +6234,14 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -6787,7 +6787,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7354,7 +7354,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E352" t="inlineStr"/>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
@@ -8047,42 +8047,42 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
@@ -8236,16 +8236,16 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -8257,16 +8257,16 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -8740,42 +8740,42 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E398" t="inlineStr"/>
@@ -9055,21 +9055,21 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E412" t="inlineStr"/>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -9097,7 +9097,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -9106,12 +9106,12 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -9181,11 +9181,11 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>2015</v>
+        <v>2024</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9195,18 +9195,18 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
@@ -10084,16 +10084,16 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -10105,16 +10105,16 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -10701,11 +10701,11 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -10724,7 +10724,7 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -10839,11 +10839,11 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -11368,16 +11368,16 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -11414,16 +11414,16 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -11460,16 +11460,16 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Inezgane Ait Melloul</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -11483,16 +11483,16 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Inezgane Ait Melloul</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -12840,7 +12840,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E581" t="n">
@@ -12863,7 +12863,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E582" t="n">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -13047,7 +13047,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -13070,7 +13070,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -13093,21 +13093,21 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E592" t="n">
@@ -13116,21 +13116,21 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E593" t="n">
@@ -13162,7 +13162,7 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -13300,11 +13300,11 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E601" t="n">
@@ -13323,11 +13323,11 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E602" t="n">
@@ -13350,12 +13350,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -13369,21 +13369,21 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E604" t="n">
@@ -13392,11 +13392,11 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E605" t="n">
@@ -13507,7 +13507,7 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E610" t="n">
@@ -13530,7 +13530,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E611" t="n">
@@ -13691,16 +13691,16 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -13714,16 +13714,16 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -13737,11 +13737,11 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E620" t="n">
@@ -13760,11 +13760,11 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E621" t="n">
@@ -13806,11 +13806,11 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -13829,11 +13829,11 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -13921,7 +13921,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Féminin</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E628" t="n">
@@ -13944,21 +13944,21 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>Tiznit</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E629" t="n">
@@ -13967,21 +13967,21 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Féminin</t>
         </is>
       </c>
       <c r="E630" t="n">
@@ -13990,11 +13990,11 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Tiznit</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -14059,16 +14059,16 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Urbain</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -14082,21 +14082,21 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Urbain</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E635" t="n">
@@ -14105,11 +14105,11 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E636" t="n">
@@ -14289,21 +14289,21 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E644" t="n">
@@ -14312,21 +14312,21 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E645" t="n">
@@ -14335,7 +14335,7 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -14611,7 +14611,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -14634,7 +14634,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>Agadir Ida Ou Tanane</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E661" t="n">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Agadir Ida Ou Tanane</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E662" t="n">
@@ -14795,21 +14795,21 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Taroudannt</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E666" t="n">
@@ -14841,21 +14841,21 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Taroudannt</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Rural</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E668" t="n">
@@ -14864,11 +14864,11 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E669" t="n">
@@ -14887,11 +14887,11 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Chtouka- Ait Baha</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E670" t="n">
@@ -14910,11 +14910,11 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>Chtouka- Ait Baha</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -14933,11 +14933,11 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E672" t="n">
@@ -14956,7 +14956,7 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E673" t="n">
@@ -14979,11 +14979,11 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -15025,11 +15025,11 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>Souss-Massa</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Masculin</t>
         </is>
       </c>
       <c r="E676" t="n">
@@ -15048,11 +15048,11 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Souss-Massa</t>
+          <t>National</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -15071,7 +15071,7 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Masculin</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E678" t="n">
